--- a/data/MK_ECB_DATA_20260807.xlsx
+++ b/data/MK_ECB_DATA_20260807.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E684"/>
+  <dimension ref="A1:E694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2044,25 +2044,25 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF32.CR</t>
+          <t>EST.B.EU000A2QQF24.CR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>€STR 3개월 복리평균</t>
+          <t>€STR 1개월 복리평균</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260807</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.93597</v>
+        <v>2.1862</v>
       </c>
     </row>
     <row r="72">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -2104,11 +2104,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.93598</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="74">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.93603</v>
+        <v>1.93598</v>
       </c>
     </row>
     <row r="75">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.93607</v>
+        <v>1.93603</v>
       </c>
     </row>
     <row r="76">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.93597</v>
+        <v>1.93607</v>
       </c>
     </row>
     <row r="77">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1.93598</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="78">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.93596</v>
+        <v>1.93598</v>
       </c>
     </row>
     <row r="79">
@@ -2242,11 +2242,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.93597</v>
+        <v>1.93596</v>
       </c>
     </row>
     <row r="80">
@@ -2265,11 +2265,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.93601</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="81">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.93597</v>
+        <v>1.93601</v>
       </c>
     </row>
     <row r="82">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2334,11 +2334,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.93592</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="84">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1.93597</v>
+        <v>1.93592</v>
       </c>
     </row>
     <row r="85">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1.93603</v>
+        <v>1.93597</v>
       </c>
     </row>
     <row r="86">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.93582</v>
+        <v>1.93603</v>
       </c>
     </row>
     <row r="87">
@@ -2426,11 +2426,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.9358</v>
+        <v>1.93582</v>
       </c>
     </row>
     <row r="88">
@@ -2449,11 +2449,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.93577</v>
+        <v>1.9358</v>
       </c>
     </row>
     <row r="89">
@@ -2472,11 +2472,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1.93583</v>
+        <v>1.93577</v>
       </c>
     </row>
     <row r="90">
@@ -2495,11 +2495,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.9359</v>
+        <v>1.93583</v>
       </c>
     </row>
     <row r="91">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1.93595</v>
+        <v>1.9359</v>
       </c>
     </row>
     <row r="93">
@@ -2564,11 +2564,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.93593</v>
+        <v>1.93595</v>
       </c>
     </row>
     <row r="94">
@@ -2587,11 +2587,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1.93589</v>
+        <v>1.93593</v>
       </c>
     </row>
     <row r="95">
@@ -2610,11 +2610,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.93588</v>
+        <v>1.93589</v>
       </c>
     </row>
     <row r="96">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.93594</v>
+        <v>1.93588</v>
       </c>
     </row>
     <row r="97">
@@ -2656,11 +2656,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.93576</v>
+        <v>1.93594</v>
       </c>
     </row>
     <row r="98">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1.93574</v>
+        <v>1.93576</v>
       </c>
     </row>
     <row r="99">
@@ -2702,11 +2702,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1.93571</v>
+        <v>1.93574</v>
       </c>
     </row>
     <row r="100">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1.9358</v>
+        <v>1.93571</v>
       </c>
     </row>
     <row r="102">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1.93573</v>
+        <v>1.9358</v>
       </c>
     </row>
     <row r="103">
@@ -2794,11 +2794,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1.93572</v>
+        <v>1.93573</v>
       </c>
     </row>
     <row r="104">
@@ -2817,11 +2817,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.93845</v>
+        <v>1.93572</v>
       </c>
     </row>
     <row r="105">
@@ -2840,11 +2840,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1.94115</v>
+        <v>1.93845</v>
       </c>
     </row>
     <row r="106">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1.94912</v>
+        <v>1.94115</v>
       </c>
     </row>
     <row r="107">
@@ -2886,11 +2886,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1.952</v>
+        <v>1.94912</v>
       </c>
     </row>
     <row r="108">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1.95474</v>
+        <v>1.952</v>
       </c>
     </row>
     <row r="109">
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1.95746</v>
+        <v>1.95474</v>
       </c>
     </row>
     <row r="110">
@@ -2955,11 +2955,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1.96022</v>
+        <v>1.95746</v>
       </c>
     </row>
     <row r="111">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1.96783</v>
+        <v>1.96022</v>
       </c>
     </row>
     <row r="112">
@@ -3001,11 +3001,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.9712</v>
+        <v>1.96783</v>
       </c>
     </row>
     <row r="113">
@@ -3024,11 +3024,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.97432</v>
+        <v>1.9712</v>
       </c>
     </row>
     <row r="114">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1.97711</v>
+        <v>1.97432</v>
       </c>
     </row>
     <row r="115">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.97947</v>
+        <v>1.97711</v>
       </c>
     </row>
     <row r="116">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1.98624</v>
+        <v>1.97947</v>
       </c>
     </row>
     <row r="117">
@@ -3116,11 +3116,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1.99102</v>
+        <v>1.98624</v>
       </c>
     </row>
     <row r="118">
@@ -3139,11 +3139,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1.99379</v>
+        <v>1.99102</v>
       </c>
     </row>
     <row r="119">
@@ -3162,11 +3162,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1.99656</v>
+        <v>1.99379</v>
       </c>
     </row>
     <row r="120">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1.99934</v>
+        <v>1.99656</v>
       </c>
     </row>
     <row r="121">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2.00762</v>
+        <v>1.99934</v>
       </c>
     </row>
     <row r="122">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2.0104</v>
+        <v>2.00762</v>
       </c>
     </row>
     <row r="123">
@@ -3254,11 +3254,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2.01318</v>
+        <v>2.0104</v>
       </c>
     </row>
     <row r="124">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2.01597</v>
+        <v>2.01318</v>
       </c>
     </row>
     <row r="125">
@@ -3300,11 +3300,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2.01876</v>
+        <v>2.01597</v>
       </c>
     </row>
     <row r="126">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2.02718</v>
+        <v>2.01876</v>
       </c>
     </row>
     <row r="127">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2.02997</v>
+        <v>2.02718</v>
       </c>
     </row>
     <row r="128">
@@ -3369,11 +3369,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2.03274</v>
+        <v>2.02997</v>
       </c>
     </row>
     <row r="129">
@@ -3392,11 +3392,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2.03554</v>
+        <v>2.03274</v>
       </c>
     </row>
     <row r="130">
@@ -3415,11 +3415,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2.03832</v>
+        <v>2.03554</v>
       </c>
     </row>
     <row r="131">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2.0467</v>
+        <v>2.03832</v>
       </c>
     </row>
     <row r="132">
@@ -3461,11 +3461,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2.0495</v>
+        <v>2.0467</v>
       </c>
     </row>
     <row r="133">
@@ -3484,11 +3484,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2.05228</v>
+        <v>2.0495</v>
       </c>
     </row>
     <row r="134">
@@ -3507,11 +3507,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2.05508</v>
+        <v>2.05228</v>
       </c>
     </row>
     <row r="135">
@@ -3530,11 +3530,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2.05661</v>
+        <v>2.05508</v>
       </c>
     </row>
     <row r="136">
@@ -3553,11 +3553,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2.06631</v>
+        <v>2.05661</v>
       </c>
     </row>
     <row r="137">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2.06773</v>
+        <v>2.06631</v>
       </c>
     </row>
     <row r="138">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2.07049</v>
+        <v>2.06773</v>
       </c>
     </row>
     <row r="139">
@@ -3622,57 +3622,57 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2.07325</v>
+        <v>2.07049</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2X2A25.WT</t>
+          <t>EST.B.EU000A2QQF32.CR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>€STR 금리</t>
+          <t>€STR 3개월 복리평균</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1.932</v>
+        <v>2.07325</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2X2A25.WT</t>
+          <t>EST.B.EU000A2QQF32.CR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>€STR 금리</t>
+          <t>€STR 3개월 복리평균</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260807</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1.932</v>
+        <v>2.07603</v>
       </c>
     </row>
     <row r="142">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1.931</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="143">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1.93</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="144">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="145">
@@ -3760,11 +3760,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="146">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1.928</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="148">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1.93</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="149">
@@ -3852,11 +3852,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1.931</v>
+        <v>1.928</v>
       </c>
     </row>
     <row r="150">
@@ -3875,11 +3875,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="151">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="152">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1.932</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="154">
@@ -3967,11 +3967,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="155">
@@ -3990,11 +3990,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1.931</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="156">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1.932</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="157">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1.932</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="158">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1.933</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="159">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1.93</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="160">
@@ -4105,11 +4105,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1.931</v>
+        <v>1.933</v>
       </c>
     </row>
     <row r="161">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1.932</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="162">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1.933</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="164">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4220,11 +4220,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1.93</v>
+        <v>1.933</v>
       </c>
     </row>
     <row r="166">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1.93</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="167">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="169">
@@ -4312,11 +4312,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1.931</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="170">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2.182</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2.18</v>
+        <v>1.931</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2.181</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2.181</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2.182</v>
+        <v>2.181</v>
       </c>
     </row>
     <row r="177">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4519,11 +4519,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2.183</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="179">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4565,11 +4565,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2.182</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2.182</v>
+        <v>2.181</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2.183</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2.183</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="184">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2.182</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2.182</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="187">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2.184</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="191">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2.184</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="192">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2.185</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="194">
@@ -4887,11 +4887,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2.186</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="195">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2.184</v>
+        <v>2.185</v>
       </c>
     </row>
     <row r="196">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2.183</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="197">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2.185</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2.186</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="200">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2.184</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="202">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2.185</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="204">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2.184</v>
+        <v>2.185</v>
       </c>
     </row>
     <row r="205">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2.185</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="207">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5195,71 +5195,71 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF08.CI</t>
+          <t>EST.B.EU000A2X2A25.WT</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>€STR 복리지수</t>
+          <t>€STR 금리</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>108.924487</v>
+        <v>2.185</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF08.CI</t>
+          <t>EST.B.EU000A2X2A25.WT</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>€STR 복리지수</t>
+          <t>€STR 금리</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>108.930332</v>
+        <v>2.185</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>EST.B.EU000A2QQF08.CI</t>
+          <t>EST.B.EU000A2X2A25.WT</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>€STR 복리지수</t>
+          <t>€STR 금리</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>108.936178</v>
+        <v>2.185</v>
       </c>
     </row>
     <row r="211">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>108.942021</v>
+        <v>108.924487</v>
       </c>
     </row>
     <row r="212">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>108.947862</v>
+        <v>108.930332</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>108.965375</v>
+        <v>108.936178</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>108.97122</v>
+        <v>108.942021</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>108.977059</v>
+        <v>108.947862</v>
       </c>
     </row>
     <row r="216">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>108.982895</v>
+        <v>108.965375</v>
       </c>
     </row>
     <row r="217">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>108.988738</v>
+        <v>108.97122</v>
       </c>
     </row>
     <row r="218">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>109.006276</v>
+        <v>108.977059</v>
       </c>
     </row>
     <row r="219">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>109.012123</v>
+        <v>108.982895</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>109.017964</v>
+        <v>108.988738</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>109.023812</v>
+        <v>109.006276</v>
       </c>
     </row>
     <row r="222">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>109.029663</v>
+        <v>109.012123</v>
       </c>
     </row>
     <row r="223">
@@ -5554,11 +5554,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>109.047189</v>
+        <v>109.017964</v>
       </c>
     </row>
     <row r="224">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>109.053039</v>
+        <v>109.023812</v>
       </c>
     </row>
     <row r="225">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>109.058891</v>
+        <v>109.029663</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>109.064744</v>
+        <v>109.047189</v>
       </c>
     </row>
     <row r="227">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>109.0706</v>
+        <v>109.053039</v>
       </c>
     </row>
     <row r="228">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>109.088142</v>
+        <v>109.058891</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>109.093994</v>
+        <v>109.064744</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>109.099848</v>
+        <v>109.0706</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>109.1057</v>
+        <v>109.088142</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>109.111559</v>
+        <v>109.093994</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>109.129117</v>
+        <v>109.099848</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>109.134967</v>
+        <v>109.1057</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>109.140818</v>
+        <v>109.111559</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>109.146669</v>
+        <v>109.129117</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>109.152524</v>
+        <v>109.134967</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>109.170088</v>
+        <v>109.140818</v>
       </c>
     </row>
     <row r="239">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>109.175944</v>
+        <v>109.146669</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>109.1818</v>
+        <v>109.152524</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>109.188418</v>
+        <v>109.170088</v>
       </c>
     </row>
     <row r="242">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>109.195029</v>
+        <v>109.175944</v>
       </c>
     </row>
     <row r="243">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>109.214876</v>
+        <v>109.1818</v>
       </c>
     </row>
     <row r="244">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>109.221492</v>
+        <v>109.188418</v>
       </c>
     </row>
     <row r="245">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>109.228112</v>
+        <v>109.195029</v>
       </c>
     </row>
     <row r="246">
@@ -6083,11 +6083,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>109.23473</v>
+        <v>109.214876</v>
       </c>
     </row>
     <row r="247">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>109.241354</v>
+        <v>109.221492</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>109.261208</v>
+        <v>109.228112</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>109.267831</v>
+        <v>109.23473</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>109.274454</v>
+        <v>109.241354</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>109.28108</v>
+        <v>109.261208</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>109.287706</v>
+        <v>109.267831</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>109.307588</v>
+        <v>109.274454</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>109.314213</v>
+        <v>109.28108</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>109.320839</v>
+        <v>109.287706</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>109.327465</v>
+        <v>109.307588</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>109.334091</v>
+        <v>109.314213</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>109.353972</v>
+        <v>109.320839</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>109.360606</v>
+        <v>109.327465</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>109.36724</v>
+        <v>109.334091</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>109.373875</v>
+        <v>109.353972</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>109.380514</v>
+        <v>109.360606</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>109.400439</v>
+        <v>109.36724</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>109.407076</v>
+        <v>109.373875</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>109.413711</v>
+        <v>109.380514</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>109.420348</v>
+        <v>109.400439</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>109.426989</v>
+        <v>109.407076</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>109.446923</v>
+        <v>109.413711</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>109.453566</v>
+        <v>109.420348</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>109.460206</v>
+        <v>109.426989</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>109.46685</v>
+        <v>109.446923</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>109.473494</v>
+        <v>109.453566</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>109.493418</v>
+        <v>109.460206</v>
       </c>
     </row>
     <row r="274">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>109.500064</v>
+        <v>109.46685</v>
       </c>
     </row>
     <row r="275">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>109.50671</v>
+        <v>109.473494</v>
       </c>
     </row>
     <row r="276">
@@ -6773,103 +6773,103 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>109.513356</v>
+        <v>109.493418</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>2.604738</v>
+        <v>109.500064</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2.602065</v>
+        <v>109.50671</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>2.50443</v>
+        <v>109.513356</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
+          <t>EST.B.EU000A2QQF08.CI</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>유로존 국채금리 1년</t>
+          <t>€STR 복리지수</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260807</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>2.488514</v>
+        <v>109.520003</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>2.514596</v>
+        <v>2.604738</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>2.553344</v>
+        <v>2.602065</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>2.600826</v>
+        <v>2.50443</v>
       </c>
     </row>
     <row r="284">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>2.594349</v>
+        <v>2.488514</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>2.57128</v>
+        <v>2.514596</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>2.617938</v>
+        <v>2.553344</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>2.580883</v>
+        <v>2.600826</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>2.606135</v>
+        <v>2.594349</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>2.593521</v>
+        <v>2.57128</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2.574793</v>
+        <v>2.617938</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>2.535177</v>
+        <v>2.580883</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>2.462774</v>
+        <v>2.606135</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>2.50502</v>
+        <v>2.593521</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>2.500937</v>
+        <v>2.574793</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>2.526205</v>
+        <v>2.535177</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>2.500537</v>
+        <v>2.462774</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>2.577046</v>
+        <v>2.50502</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>2.558293</v>
+        <v>2.500937</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>2.579685</v>
+        <v>2.526205</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>2.575429</v>
+        <v>2.500537</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2.595465</v>
+        <v>2.577046</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>2.610515</v>
+        <v>2.558293</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>2.599927</v>
+        <v>2.579685</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2.623955</v>
+        <v>2.575429</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2.615212</v>
+        <v>2.595465</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2.576759</v>
+        <v>2.610515</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2.527404</v>
+        <v>2.599927</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2.530488</v>
+        <v>2.623955</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2.542237</v>
+        <v>2.615212</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2.560441</v>
+        <v>2.576759</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>2.573815</v>
+        <v>2.527404</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>2.542998</v>
+        <v>2.530488</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>2.513387</v>
+        <v>2.542237</v>
       </c>
     </row>
     <row r="314">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>2.503837</v>
+        <v>2.560441</v>
       </c>
     </row>
     <row r="315">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>2.494744</v>
+        <v>2.573815</v>
       </c>
     </row>
     <row r="316">
@@ -7693,11 +7693,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>2.491015</v>
+        <v>2.542998</v>
       </c>
     </row>
     <row r="317">
@@ -7716,11 +7716,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>2.501607</v>
+        <v>2.513387</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>2.496523</v>
+        <v>2.503837</v>
       </c>
     </row>
     <row r="319">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2.49067</v>
+        <v>2.494744</v>
       </c>
     </row>
     <row r="320">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>2.467318</v>
+        <v>2.491015</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>2.481722</v>
+        <v>2.501607</v>
       </c>
     </row>
     <row r="322">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>2.485331</v>
+        <v>2.496523</v>
       </c>
     </row>
     <row r="323">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>2.51834</v>
+        <v>2.49067</v>
       </c>
     </row>
     <row r="324">
@@ -7877,11 +7877,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>2.600055</v>
+        <v>2.467318</v>
       </c>
     </row>
     <row r="325">
@@ -7900,11 +7900,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>2.596287</v>
+        <v>2.481722</v>
       </c>
     </row>
     <row r="326">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>2.597534</v>
+        <v>2.485331</v>
       </c>
     </row>
     <row r="327">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>2.630303</v>
+        <v>2.51834</v>
       </c>
     </row>
     <row r="328">
@@ -7969,11 +7969,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>2.661163</v>
+        <v>2.600055</v>
       </c>
     </row>
     <row r="329">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2.653143</v>
+        <v>2.596287</v>
       </c>
     </row>
     <row r="330">
@@ -8015,11 +8015,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2.674195</v>
+        <v>2.597534</v>
       </c>
     </row>
     <row r="331">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2.675087</v>
+        <v>2.630303</v>
       </c>
     </row>
     <row r="332">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>2.681168</v>
+        <v>2.661163</v>
       </c>
     </row>
     <row r="333">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>2.696713</v>
+        <v>2.653143</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>2.708082</v>
+        <v>2.674195</v>
       </c>
     </row>
     <row r="335">
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2.739593</v>
+        <v>2.675087</v>
       </c>
     </row>
     <row r="336">
@@ -8153,11 +8153,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>2.717336</v>
+        <v>2.681168</v>
       </c>
     </row>
     <row r="337">
@@ -8176,11 +8176,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2.696091</v>
+        <v>2.696713</v>
       </c>
     </row>
     <row r="338">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>2.680129</v>
+        <v>2.708082</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>2.70197</v>
+        <v>2.739593</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>2.683152</v>
+        <v>2.717336</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>2.708539</v>
+        <v>2.696091</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>2.675089</v>
+        <v>2.680129</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2.640302</v>
+        <v>2.70197</v>
       </c>
     </row>
     <row r="344">
@@ -8337,126 +8337,126 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>2.642342</v>
+        <v>2.683152</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>2.709578</v>
+        <v>2.708539</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>2.713377</v>
+        <v>2.675089</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>2.580816</v>
+        <v>2.640302</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>2.563197</v>
+        <v>2.642342</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_1Y</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>유로존 국채금리 2년</t>
+          <t>유로존 국채금리 1년</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2.590769</v>
+        <v>2.648283</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>2.651872</v>
+        <v>2.709578</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>2.734067</v>
+        <v>2.713377</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>2.720401</v>
+        <v>2.580816</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>2.673633</v>
+        <v>2.563197</v>
       </c>
     </row>
     <row r="354">
@@ -8567,11 +8567,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>2.759799</v>
+        <v>2.590769</v>
       </c>
     </row>
     <row r="355">
@@ -8590,11 +8590,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2.701019</v>
+        <v>2.651872</v>
       </c>
     </row>
     <row r="356">
@@ -8613,11 +8613,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>2.758581</v>
+        <v>2.734067</v>
       </c>
     </row>
     <row r="357">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>2.732917</v>
+        <v>2.720401</v>
       </c>
     </row>
     <row r="358">
@@ -8659,11 +8659,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>2.690643</v>
+        <v>2.673633</v>
       </c>
     </row>
     <row r="359">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2.649058</v>
+        <v>2.759799</v>
       </c>
     </row>
     <row r="360">
@@ -8705,11 +8705,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2.550151</v>
+        <v>2.701019</v>
       </c>
     </row>
     <row r="361">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2.600158</v>
+        <v>2.758581</v>
       </c>
     </row>
     <row r="362">
@@ -8751,11 +8751,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2.584193</v>
+        <v>2.732917</v>
       </c>
     </row>
     <row r="363">
@@ -8774,11 +8774,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2.60767</v>
+        <v>2.690643</v>
       </c>
     </row>
     <row r="364">
@@ -8797,11 +8797,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2.573921</v>
+        <v>2.649058</v>
       </c>
     </row>
     <row r="365">
@@ -8820,11 +8820,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2.664843</v>
+        <v>2.550151</v>
       </c>
     </row>
     <row r="366">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>2.631211</v>
+        <v>2.600158</v>
       </c>
     </row>
     <row r="367">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2.668913</v>
+        <v>2.584193</v>
       </c>
     </row>
     <row r="368">
@@ -8889,11 +8889,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>2.667137</v>
+        <v>2.60767</v>
       </c>
     </row>
     <row r="369">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>2.690449</v>
+        <v>2.573921</v>
       </c>
     </row>
     <row r="370">
@@ -8935,11 +8935,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>2.70087</v>
+        <v>2.664843</v>
       </c>
     </row>
     <row r="371">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>2.687806</v>
+        <v>2.631211</v>
       </c>
     </row>
     <row r="372">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>2.718796</v>
+        <v>2.668913</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>2.687187</v>
+        <v>2.667137</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>2.661527</v>
+        <v>2.690449</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>2.585514</v>
+        <v>2.70087</v>
       </c>
     </row>
     <row r="376">
@@ -9073,11 +9073,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>2.586505</v>
+        <v>2.687806</v>
       </c>
     </row>
     <row r="377">
@@ -9096,11 +9096,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2.599634</v>
+        <v>2.718796</v>
       </c>
     </row>
     <row r="378">
@@ -9119,11 +9119,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>2.625835</v>
+        <v>2.687187</v>
       </c>
     </row>
     <row r="379">
@@ -9142,11 +9142,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>2.653029</v>
+        <v>2.661527</v>
       </c>
     </row>
     <row r="380">
@@ -9165,11 +9165,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>2.611516</v>
+        <v>2.585514</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>2.579206</v>
+        <v>2.586505</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>2.567358</v>
+        <v>2.599634</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>2.550469</v>
+        <v>2.625835</v>
       </c>
     </row>
     <row r="384">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>2.541062</v>
+        <v>2.653029</v>
       </c>
     </row>
     <row r="385">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>2.551573</v>
+        <v>2.611516</v>
       </c>
     </row>
     <row r="386">
@@ -9303,11 +9303,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>2.546422</v>
+        <v>2.579206</v>
       </c>
     </row>
     <row r="387">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>2.550091</v>
+        <v>2.567358</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>2.533759</v>
+        <v>2.550469</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>2.559161</v>
+        <v>2.541062</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>2.55997</v>
+        <v>2.551573</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>2.604448</v>
+        <v>2.546422</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>2.702377</v>
+        <v>2.550091</v>
       </c>
     </row>
     <row r="393">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2.690162</v>
+        <v>2.533759</v>
       </c>
     </row>
     <row r="394">
@@ -9487,11 +9487,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>2.679635</v>
+        <v>2.559161</v>
       </c>
     </row>
     <row r="395">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>2.728376</v>
+        <v>2.55997</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>2.768288</v>
+        <v>2.604448</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>2.769299</v>
+        <v>2.702377</v>
       </c>
     </row>
     <row r="398">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>2.792324</v>
+        <v>2.690162</v>
       </c>
     </row>
     <row r="399">
@@ -9602,11 +9602,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>2.795659</v>
+        <v>2.679635</v>
       </c>
     </row>
     <row r="400">
@@ -9625,11 +9625,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>2.797507</v>
+        <v>2.728376</v>
       </c>
     </row>
     <row r="401">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>2.833711</v>
+        <v>2.768288</v>
       </c>
     </row>
     <row r="402">
@@ -9671,11 +9671,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>2.851023</v>
+        <v>2.769299</v>
       </c>
     </row>
     <row r="403">
@@ -9694,11 +9694,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>2.895706</v>
+        <v>2.792324</v>
       </c>
     </row>
     <row r="404">
@@ -9717,11 +9717,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>2.863655</v>
+        <v>2.795659</v>
       </c>
     </row>
     <row r="405">
@@ -9740,11 +9740,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>2.81802</v>
+        <v>2.797507</v>
       </c>
     </row>
     <row r="406">
@@ -9763,11 +9763,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>2.797378</v>
+        <v>2.833711</v>
       </c>
     </row>
     <row r="407">
@@ -9786,11 +9786,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>2.828056</v>
+        <v>2.851023</v>
       </c>
     </row>
     <row r="408">
@@ -9809,11 +9809,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>2.804105</v>
+        <v>2.895706</v>
       </c>
     </row>
     <row r="409">
@@ -9832,11 +9832,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>2.84114</v>
+        <v>2.863655</v>
       </c>
     </row>
     <row r="410">
@@ -9855,11 +9855,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>2.79236</v>
+        <v>2.81802</v>
       </c>
     </row>
     <row r="411">
@@ -9878,11 +9878,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>2.736657</v>
+        <v>2.797378</v>
       </c>
     </row>
     <row r="412">
@@ -9901,149 +9901,149 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>2.75198</v>
+        <v>2.828056</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>2.785695</v>
+        <v>2.804105</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>2.791931</v>
+        <v>2.84114</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>2.660543</v>
+        <v>2.79236</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>2.647172</v>
+        <v>2.736657</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>2.668906</v>
+        <v>2.75198</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_2Y</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>유로존 국채금리 3년</t>
+          <t>유로존 국채금리 2년</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>2.727433</v>
+        <v>2.755483</v>
       </c>
     </row>
     <row r="419">
@@ -10062,11 +10062,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>2.812236</v>
+        <v>2.785695</v>
       </c>
     </row>
     <row r="420">
@@ -10085,11 +10085,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>2.800452</v>
+        <v>2.791931</v>
       </c>
     </row>
     <row r="421">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>2.746714</v>
+        <v>2.660543</v>
       </c>
     </row>
     <row r="422">
@@ -10131,11 +10131,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>2.846863</v>
+        <v>2.647172</v>
       </c>
     </row>
     <row r="423">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>2.787952</v>
+        <v>2.668906</v>
       </c>
     </row>
     <row r="424">
@@ -10177,11 +10177,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>2.854181</v>
+        <v>2.727433</v>
       </c>
     </row>
     <row r="425">
@@ -10200,11 +10200,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>2.823594</v>
+        <v>2.812236</v>
       </c>
     </row>
     <row r="426">
@@ -10223,11 +10223,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>2.775414</v>
+        <v>2.800452</v>
       </c>
     </row>
     <row r="427">
@@ -10246,11 +10246,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>2.73301</v>
+        <v>2.746714</v>
       </c>
     </row>
     <row r="428">
@@ -10269,11 +10269,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>2.632702</v>
+        <v>2.846863</v>
       </c>
     </row>
     <row r="429">
@@ -10292,11 +10292,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>2.685019</v>
+        <v>2.787952</v>
       </c>
     </row>
     <row r="430">
@@ -10315,11 +10315,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>2.665718</v>
+        <v>2.854181</v>
       </c>
     </row>
     <row r="431">
@@ -10338,11 +10338,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>2.685927</v>
+        <v>2.823594</v>
       </c>
     </row>
     <row r="432">
@@ -10361,11 +10361,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>2.653732</v>
+        <v>2.775414</v>
       </c>
     </row>
     <row r="433">
@@ -10384,11 +10384,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>2.737626</v>
+        <v>2.73301</v>
       </c>
     </row>
     <row r="434">
@@ -10407,11 +10407,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>2.695968</v>
+        <v>2.632702</v>
       </c>
     </row>
     <row r="435">
@@ -10430,11 +10430,11 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>2.739566</v>
+        <v>2.685019</v>
       </c>
     </row>
     <row r="436">
@@ -10453,11 +10453,11 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>2.742955</v>
+        <v>2.665718</v>
       </c>
     </row>
     <row r="437">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>2.76777</v>
+        <v>2.685927</v>
       </c>
     </row>
     <row r="438">
@@ -10499,11 +10499,11 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>2.775779</v>
+        <v>2.653732</v>
       </c>
     </row>
     <row r="439">
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>2.765536</v>
+        <v>2.737626</v>
       </c>
     </row>
     <row r="440">
@@ -10545,11 +10545,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>2.79679</v>
+        <v>2.695968</v>
       </c>
     </row>
     <row r="441">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>2.759517</v>
+        <v>2.739566</v>
       </c>
     </row>
     <row r="442">
@@ -10591,11 +10591,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>2.740071</v>
+        <v>2.742955</v>
       </c>
     </row>
     <row r="443">
@@ -10614,11 +10614,11 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>2.664179</v>
+        <v>2.76777</v>
       </c>
     </row>
     <row r="444">
@@ -10637,11 +10637,11 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>2.660499</v>
+        <v>2.775779</v>
       </c>
     </row>
     <row r="445">
@@ -10660,11 +10660,11 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>2.66923</v>
+        <v>2.765536</v>
       </c>
     </row>
     <row r="446">
@@ -10683,11 +10683,11 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>2.694761</v>
+        <v>2.79679</v>
       </c>
     </row>
     <row r="447">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>2.728076</v>
+        <v>2.759517</v>
       </c>
     </row>
     <row r="448">
@@ -10729,11 +10729,11 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>2.688614</v>
+        <v>2.740071</v>
       </c>
     </row>
     <row r="449">
@@ -10752,11 +10752,11 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>2.659069</v>
+        <v>2.664179</v>
       </c>
     </row>
     <row r="450">
@@ -10775,11 +10775,11 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>2.642481</v>
+        <v>2.660499</v>
       </c>
     </row>
     <row r="451">
@@ -10798,11 +10798,11 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>2.625755</v>
+        <v>2.66923</v>
       </c>
     </row>
     <row r="452">
@@ -10821,11 +10821,11 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>2.618788</v>
+        <v>2.694761</v>
       </c>
     </row>
     <row r="453">
@@ -10844,11 +10844,11 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>2.629515</v>
+        <v>2.728076</v>
       </c>
     </row>
     <row r="454">
@@ -10867,11 +10867,11 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>2.625196</v>
+        <v>2.688614</v>
       </c>
     </row>
     <row r="455">
@@ -10890,11 +10890,11 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>2.637535</v>
+        <v>2.659069</v>
       </c>
     </row>
     <row r="456">
@@ -10913,11 +10913,11 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>2.62789</v>
+        <v>2.642481</v>
       </c>
     </row>
     <row r="457">
@@ -10936,11 +10936,11 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>2.65319</v>
+        <v>2.625755</v>
       </c>
     </row>
     <row r="458">
@@ -10959,11 +10959,11 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>2.653312</v>
+        <v>2.618788</v>
       </c>
     </row>
     <row r="459">
@@ -10982,11 +10982,11 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>2.698194</v>
+        <v>2.629515</v>
       </c>
     </row>
     <row r="460">
@@ -11005,11 +11005,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>2.795557</v>
+        <v>2.625196</v>
       </c>
     </row>
     <row r="461">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>2.77975</v>
+        <v>2.637535</v>
       </c>
     </row>
     <row r="462">
@@ -11051,11 +11051,11 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>2.762221</v>
+        <v>2.62789</v>
       </c>
     </row>
     <row r="463">
@@ -11074,11 +11074,11 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>2.807167</v>
+        <v>2.65319</v>
       </c>
     </row>
     <row r="464">
@@ -11097,11 +11097,11 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>2.846448</v>
+        <v>2.653312</v>
       </c>
     </row>
     <row r="465">
@@ -11120,11 +11120,11 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>2.854227</v>
+        <v>2.698194</v>
       </c>
     </row>
     <row r="466">
@@ -11143,11 +11143,11 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>2.87901</v>
+        <v>2.795557</v>
       </c>
     </row>
     <row r="467">
@@ -11166,11 +11166,11 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>2.878146</v>
+        <v>2.77975</v>
       </c>
     </row>
     <row r="468">
@@ -11189,11 +11189,11 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>2.878026</v>
+        <v>2.762221</v>
       </c>
     </row>
     <row r="469">
@@ -11212,11 +11212,11 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>2.921818</v>
+        <v>2.807167</v>
       </c>
     </row>
     <row r="470">
@@ -11235,11 +11235,11 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>2.938639</v>
+        <v>2.846448</v>
       </c>
     </row>
     <row r="471">
@@ -11258,11 +11258,11 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>2.984282</v>
+        <v>2.854227</v>
       </c>
     </row>
     <row r="472">
@@ -11281,11 +11281,11 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>2.950427</v>
+        <v>2.87901</v>
       </c>
     </row>
     <row r="473">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>2.894467</v>
+        <v>2.878146</v>
       </c>
     </row>
     <row r="474">
@@ -11327,11 +11327,11 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>2.875853</v>
+        <v>2.878026</v>
       </c>
     </row>
     <row r="475">
@@ -11350,11 +11350,11 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>2.905911</v>
+        <v>2.921818</v>
       </c>
     </row>
     <row r="476">
@@ -11373,11 +11373,11 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>2.889878</v>
+        <v>2.938639</v>
       </c>
     </row>
     <row r="477">
@@ -11396,11 +11396,11 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>2.928374</v>
+        <v>2.984282</v>
       </c>
     </row>
     <row r="478">
@@ -11419,11 +11419,11 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>2.874681</v>
+        <v>2.950427</v>
       </c>
     </row>
     <row r="479">
@@ -11442,11 +11442,11 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>2.817198</v>
+        <v>2.894467</v>
       </c>
     </row>
     <row r="480">
@@ -11465,172 +11465,172 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>2.836884</v>
+        <v>2.875853</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>3.000517</v>
+        <v>2.905911</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>3.007991</v>
+        <v>2.889878</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>2.886073</v>
+        <v>2.928374</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>2.876206</v>
+        <v>2.874681</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2.889313</v>
+        <v>2.817198</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>2.939157</v>
+        <v>2.836884</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_3Y</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>유로존 국채금리 5년</t>
+          <t>유로존 국채금리 3년</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>3.015143</v>
+        <v>2.83918</v>
       </c>
     </row>
     <row r="488">
@@ -11649,11 +11649,11 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>3.012751</v>
+        <v>3.000517</v>
       </c>
     </row>
     <row r="489">
@@ -11672,11 +11672,11 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>2.955911</v>
+        <v>3.007991</v>
       </c>
     </row>
     <row r="490">
@@ -11695,11 +11695,11 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>3.063218</v>
+        <v>2.886073</v>
       </c>
     </row>
     <row r="491">
@@ -11718,11 +11718,11 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>3.014232</v>
+        <v>2.876206</v>
       </c>
     </row>
     <row r="492">
@@ -11741,11 +11741,11 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>3.077971</v>
+        <v>2.889313</v>
       </c>
     </row>
     <row r="493">
@@ -11764,11 +11764,11 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>3.044699</v>
+        <v>2.939157</v>
       </c>
     </row>
     <row r="494">
@@ -11787,11 +11787,11 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>2.995816</v>
+        <v>3.015143</v>
       </c>
     </row>
     <row r="495">
@@ -11810,11 +11810,11 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>2.948017</v>
+        <v>3.012751</v>
       </c>
     </row>
     <row r="496">
@@ -11833,11 +11833,11 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>2.848562</v>
+        <v>2.955911</v>
       </c>
     </row>
     <row r="497">
@@ -11856,11 +11856,11 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>2.900503</v>
+        <v>3.063218</v>
       </c>
     </row>
     <row r="498">
@@ -11879,11 +11879,11 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>2.881685</v>
+        <v>3.014232</v>
       </c>
     </row>
     <row r="499">
@@ -11902,11 +11902,11 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>2.899034</v>
+        <v>3.077971</v>
       </c>
     </row>
     <row r="500">
@@ -11925,11 +11925,11 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>2.869598</v>
+        <v>3.044699</v>
       </c>
     </row>
     <row r="501">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>2.942888</v>
+        <v>2.995816</v>
       </c>
     </row>
     <row r="502">
@@ -11971,11 +11971,11 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>2.892125</v>
+        <v>2.948017</v>
       </c>
     </row>
     <row r="503">
@@ -11994,11 +11994,11 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>2.936988</v>
+        <v>2.848562</v>
       </c>
     </row>
     <row r="504">
@@ -12017,11 +12017,11 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>2.946672</v>
+        <v>2.900503</v>
       </c>
     </row>
     <row r="505">
@@ -12040,11 +12040,11 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>2.97218</v>
+        <v>2.881685</v>
       </c>
     </row>
     <row r="506">
@@ -12063,11 +12063,11 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>2.981788</v>
+        <v>2.899034</v>
       </c>
     </row>
     <row r="507">
@@ -12086,11 +12086,11 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>2.976278</v>
+        <v>2.869598</v>
       </c>
     </row>
     <row r="508">
@@ -12109,11 +12109,11 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>3.004347</v>
+        <v>2.942888</v>
       </c>
     </row>
     <row r="509">
@@ -12132,11 +12132,11 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>2.965561</v>
+        <v>2.892125</v>
       </c>
     </row>
     <row r="510">
@@ -12155,11 +12155,11 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>2.949891</v>
+        <v>2.936988</v>
       </c>
     </row>
     <row r="511">
@@ -12178,11 +12178,11 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>2.878033</v>
+        <v>2.946672</v>
       </c>
     </row>
     <row r="512">
@@ -12201,11 +12201,11 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2.866621</v>
+        <v>2.97218</v>
       </c>
     </row>
     <row r="513">
@@ -12224,11 +12224,11 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>2.868032</v>
+        <v>2.981788</v>
       </c>
     </row>
     <row r="514">
@@ -12247,11 +12247,11 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>2.886289</v>
+        <v>2.976278</v>
       </c>
     </row>
     <row r="515">
@@ -12270,11 +12270,11 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>2.926579</v>
+        <v>3.004347</v>
       </c>
     </row>
     <row r="516">
@@ -12293,11 +12293,11 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>2.892156</v>
+        <v>2.965561</v>
       </c>
     </row>
     <row r="517">
@@ -12316,11 +12316,11 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>2.863126</v>
+        <v>2.949891</v>
       </c>
     </row>
     <row r="518">
@@ -12339,11 +12339,11 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>2.839867</v>
+        <v>2.878033</v>
       </c>
     </row>
     <row r="519">
@@ -12362,11 +12362,11 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>2.824154</v>
+        <v>2.866621</v>
       </c>
     </row>
     <row r="520">
@@ -12385,11 +12385,11 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>2.824752</v>
+        <v>2.868032</v>
       </c>
     </row>
     <row r="521">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2.833752</v>
+        <v>2.886289</v>
       </c>
     </row>
     <row r="522">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>2.829627</v>
+        <v>2.926579</v>
       </c>
     </row>
     <row r="523">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>2.854952</v>
+        <v>2.892156</v>
       </c>
     </row>
     <row r="524">
@@ -12477,11 +12477,11 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>2.856888</v>
+        <v>2.863126</v>
       </c>
     </row>
     <row r="525">
@@ -12500,11 +12500,11 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>2.878062</v>
+        <v>2.839867</v>
       </c>
     </row>
     <row r="526">
@@ -12523,11 +12523,11 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>2.878889</v>
+        <v>2.824154</v>
       </c>
     </row>
     <row r="527">
@@ -12546,11 +12546,11 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>2.920893</v>
+        <v>2.824752</v>
       </c>
     </row>
     <row r="528">
@@ -12569,11 +12569,11 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E528" t="n">
-        <v>3.01509</v>
+        <v>2.833752</v>
       </c>
     </row>
     <row r="529">
@@ -12592,11 +12592,11 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>2.999744</v>
+        <v>2.829627</v>
       </c>
     </row>
     <row r="530">
@@ -12615,11 +12615,11 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>2.978557</v>
+        <v>2.854952</v>
       </c>
     </row>
     <row r="531">
@@ -12638,11 +12638,11 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>3.010327</v>
+        <v>2.856888</v>
       </c>
     </row>
     <row r="532">
@@ -12661,11 +12661,11 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>3.044602</v>
+        <v>2.878062</v>
       </c>
     </row>
     <row r="533">
@@ -12684,11 +12684,11 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>3.057975</v>
+        <v>2.878889</v>
       </c>
     </row>
     <row r="534">
@@ -12707,11 +12707,11 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E534" t="n">
-        <v>3.086044</v>
+        <v>2.920893</v>
       </c>
     </row>
     <row r="535">
@@ -12730,11 +12730,11 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E535" t="n">
-        <v>3.074213</v>
+        <v>3.01509</v>
       </c>
     </row>
     <row r="536">
@@ -12753,11 +12753,11 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E536" t="n">
-        <v>3.077336</v>
+        <v>2.999744</v>
       </c>
     </row>
     <row r="537">
@@ -12776,11 +12776,11 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E537" t="n">
-        <v>3.123908</v>
+        <v>2.978557</v>
       </c>
     </row>
     <row r="538">
@@ -12799,11 +12799,11 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>3.133803</v>
+        <v>3.010327</v>
       </c>
     </row>
     <row r="539">
@@ -12822,11 +12822,11 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>3.17204</v>
+        <v>3.044602</v>
       </c>
     </row>
     <row r="540">
@@ -12845,11 +12845,11 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>3.141233</v>
+        <v>3.057975</v>
       </c>
     </row>
     <row r="541">
@@ -12868,11 +12868,11 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>3.085289</v>
+        <v>3.086044</v>
       </c>
     </row>
     <row r="542">
@@ -12891,11 +12891,11 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>3.072788</v>
+        <v>3.074213</v>
       </c>
     </row>
     <row r="543">
@@ -12914,11 +12914,11 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>3.097739</v>
+        <v>3.077336</v>
       </c>
     </row>
     <row r="544">
@@ -12937,11 +12937,11 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>3.099874</v>
+        <v>3.123908</v>
       </c>
     </row>
     <row r="545">
@@ -12960,11 +12960,11 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>3.131762</v>
+        <v>3.133803</v>
       </c>
     </row>
     <row r="546">
@@ -12983,11 +12983,11 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>3.076516</v>
+        <v>3.17204</v>
       </c>
     </row>
     <row r="547">
@@ -13006,11 +13006,11 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>3.024112</v>
+        <v>3.141233</v>
       </c>
     </row>
     <row r="548">
@@ -13029,195 +13029,195 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>3.041739</v>
+        <v>3.085289</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>3.228543</v>
+        <v>3.072788</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>3.237712</v>
+        <v>3.097739</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>3.119151</v>
+        <v>3.099874</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E552" t="n">
-        <v>3.108997</v>
+        <v>3.131762</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>3.118124</v>
+        <v>3.076516</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>3.16475</v>
+        <v>3.024112</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>3.237417</v>
+        <v>3.041739</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_5Y</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>유로존 국채금리 7년</t>
+          <t>유로존 국채금리 5년</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>3.240594</v>
+        <v>3.044164</v>
       </c>
     </row>
     <row r="557">
@@ -13236,11 +13236,11 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>3.18189</v>
+        <v>3.228543</v>
       </c>
     </row>
     <row r="558">
@@ -13259,11 +13259,11 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>3.292831</v>
+        <v>3.237712</v>
       </c>
     </row>
     <row r="559">
@@ -13282,11 +13282,11 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>3.250782</v>
+        <v>3.119151</v>
       </c>
     </row>
     <row r="560">
@@ -13305,11 +13305,11 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>3.311581</v>
+        <v>3.108997</v>
       </c>
     </row>
     <row r="561">
@@ -13328,11 +13328,11 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>3.275978</v>
+        <v>3.118124</v>
       </c>
     </row>
     <row r="562">
@@ -13351,11 +13351,11 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>3.226414</v>
+        <v>3.16475</v>
       </c>
     </row>
     <row r="563">
@@ -13374,11 +13374,11 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>3.172951</v>
+        <v>3.237417</v>
       </c>
     </row>
     <row r="564">
@@ -13397,11 +13397,11 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E564" t="n">
-        <v>3.070373</v>
+        <v>3.240594</v>
       </c>
     </row>
     <row r="565">
@@ -13420,11 +13420,11 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E565" t="n">
-        <v>3.121809</v>
+        <v>3.18189</v>
       </c>
     </row>
     <row r="566">
@@ -13443,11 +13443,11 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E566" t="n">
-        <v>3.104055</v>
+        <v>3.292831</v>
       </c>
     </row>
     <row r="567">
@@ -13466,11 +13466,11 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>3.12121</v>
+        <v>3.250782</v>
       </c>
     </row>
     <row r="568">
@@ -13489,11 +13489,11 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>3.091758</v>
+        <v>3.311581</v>
       </c>
     </row>
     <row r="569">
@@ -13512,11 +13512,11 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>3.162397</v>
+        <v>3.275978</v>
       </c>
     </row>
     <row r="570">
@@ -13535,11 +13535,11 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>3.105972</v>
+        <v>3.226414</v>
       </c>
     </row>
     <row r="571">
@@ -13558,11 +13558,11 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>3.150735</v>
+        <v>3.172951</v>
       </c>
     </row>
     <row r="572">
@@ -13581,11 +13581,11 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>3.164004</v>
+        <v>3.070373</v>
       </c>
     </row>
     <row r="573">
@@ -13604,11 +13604,11 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>3.188864</v>
+        <v>3.121809</v>
       </c>
     </row>
     <row r="574">
@@ -13627,11 +13627,11 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>3.200686</v>
+        <v>3.104055</v>
       </c>
     </row>
     <row r="575">
@@ -13650,11 +13650,11 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>3.197992</v>
+        <v>3.12121</v>
       </c>
     </row>
     <row r="576">
@@ -13673,11 +13673,11 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>3.223329</v>
+        <v>3.091758</v>
       </c>
     </row>
     <row r="577">
@@ -13696,11 +13696,11 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E577" t="n">
-        <v>3.182662</v>
+        <v>3.162397</v>
       </c>
     </row>
     <row r="578">
@@ -13719,11 +13719,11 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>3.16864</v>
+        <v>3.105972</v>
       </c>
     </row>
     <row r="579">
@@ -13742,11 +13742,11 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>3.096218</v>
+        <v>3.150735</v>
       </c>
     </row>
     <row r="580">
@@ -13765,11 +13765,11 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>3.079783</v>
+        <v>3.164004</v>
       </c>
     </row>
     <row r="581">
@@ -13788,11 +13788,11 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>3.076564</v>
+        <v>3.188864</v>
       </c>
     </row>
     <row r="582">
@@ -13811,11 +13811,11 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>3.089147</v>
+        <v>3.200686</v>
       </c>
     </row>
     <row r="583">
@@ -13834,11 +13834,11 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>3.135827</v>
+        <v>3.197992</v>
       </c>
     </row>
     <row r="584">
@@ -13857,11 +13857,11 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>3.103015</v>
+        <v>3.223329</v>
       </c>
     </row>
     <row r="585">
@@ -13880,11 +13880,11 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>3.071323</v>
+        <v>3.182662</v>
       </c>
     </row>
     <row r="586">
@@ -13903,11 +13903,11 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>3.043622</v>
+        <v>3.16864</v>
       </c>
     </row>
     <row r="587">
@@ -13926,11 +13926,11 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>3.026814</v>
+        <v>3.096218</v>
       </c>
     </row>
     <row r="588">
@@ -13949,11 +13949,11 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>3.032928</v>
+        <v>3.079783</v>
       </c>
     </row>
     <row r="589">
@@ -13972,11 +13972,11 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>3.039436</v>
+        <v>3.076564</v>
       </c>
     </row>
     <row r="590">
@@ -13995,11 +13995,11 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>3.035337</v>
+        <v>3.089147</v>
       </c>
     </row>
     <row r="591">
@@ -14018,11 +14018,11 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>3.070159</v>
+        <v>3.135827</v>
       </c>
     </row>
     <row r="592">
@@ -14041,11 +14041,11 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>3.081383</v>
+        <v>3.103015</v>
       </c>
     </row>
     <row r="593">
@@ -14064,11 +14064,11 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>3.100713</v>
+        <v>3.071323</v>
       </c>
     </row>
     <row r="594">
@@ -14087,11 +14087,11 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>3.102715</v>
+        <v>3.043622</v>
       </c>
     </row>
     <row r="595">
@@ -14110,11 +14110,11 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>3.143962</v>
+        <v>3.026814</v>
       </c>
     </row>
     <row r="596">
@@ -14133,11 +14133,11 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>3.238182</v>
+        <v>3.032928</v>
       </c>
     </row>
     <row r="597">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>3.224814</v>
+        <v>3.039436</v>
       </c>
     </row>
     <row r="598">
@@ -14179,11 +14179,11 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>3.203147</v>
+        <v>3.035337</v>
       </c>
     </row>
     <row r="599">
@@ -14202,11 +14202,11 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>3.227624</v>
+        <v>3.070159</v>
       </c>
     </row>
     <row r="600">
@@ -14225,11 +14225,11 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>3.258737</v>
+        <v>3.081383</v>
       </c>
     </row>
     <row r="601">
@@ -14248,11 +14248,11 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>3.274647</v>
+        <v>3.100713</v>
       </c>
     </row>
     <row r="602">
@@ -14271,11 +14271,11 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>3.305365</v>
+        <v>3.102715</v>
       </c>
     </row>
     <row r="603">
@@ -14294,11 +14294,11 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>3.285927</v>
+        <v>3.143962</v>
       </c>
     </row>
     <row r="604">
@@ -14317,11 +14317,11 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>3.293337</v>
+        <v>3.238182</v>
       </c>
     </row>
     <row r="605">
@@ -14340,11 +14340,11 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>3.340835</v>
+        <v>3.224814</v>
       </c>
     </row>
     <row r="606">
@@ -14363,11 +14363,11 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>3.344391</v>
+        <v>3.203147</v>
       </c>
     </row>
     <row r="607">
@@ -14386,11 +14386,11 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>3.375894</v>
+        <v>3.227624</v>
       </c>
     </row>
     <row r="608">
@@ -14409,11 +14409,11 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>3.347836</v>
+        <v>3.258737</v>
       </c>
     </row>
     <row r="609">
@@ -14432,11 +14432,11 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>3.295641</v>
+        <v>3.274647</v>
       </c>
     </row>
     <row r="610">
@@ -14455,11 +14455,11 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>3.287519</v>
+        <v>3.305365</v>
       </c>
     </row>
     <row r="611">
@@ -14478,11 +14478,11 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E611" t="n">
-        <v>3.309462</v>
+        <v>3.285927</v>
       </c>
     </row>
     <row r="612">
@@ -14501,11 +14501,11 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E612" t="n">
-        <v>3.32385</v>
+        <v>3.293337</v>
       </c>
     </row>
     <row r="613">
@@ -14524,11 +14524,11 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>3.35007</v>
+        <v>3.340835</v>
       </c>
     </row>
     <row r="614">
@@ -14547,11 +14547,11 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>3.294375</v>
+        <v>3.344391</v>
       </c>
     </row>
     <row r="615">
@@ -14570,11 +14570,11 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260723</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>3.244491</v>
+        <v>3.375894</v>
       </c>
     </row>
     <row r="616">
@@ -14593,218 +14593,218 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260724</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>3.257593</v>
+        <v>3.347836</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260727</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>3.522383</v>
+        <v>3.295641</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260728</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>3.53446</v>
+        <v>3.287519</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260729</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>3.419526</v>
+        <v>3.309462</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260730</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>3.407866</v>
+        <v>3.32385</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260731</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>3.414486</v>
+        <v>3.35007</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260803</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>3.459084</v>
+        <v>3.294375</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260804</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>3.532267</v>
+        <v>3.244491</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>3.537955</v>
+        <v>3.257593</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_7Y</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>유로존 국채금리 10년</t>
+          <t>유로존 국채금리 7년</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>3.477861</v>
+        <v>3.260896</v>
       </c>
     </row>
     <row r="626">
@@ -14823,11 +14823,11 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>3.591227</v>
+        <v>3.522383</v>
       </c>
     </row>
     <row r="627">
@@ -14846,11 +14846,11 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>3.555828</v>
+        <v>3.53446</v>
       </c>
     </row>
     <row r="628">
@@ -14869,11 +14869,11 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>3.614122</v>
+        <v>3.419526</v>
       </c>
     </row>
     <row r="629">
@@ -14892,11 +14892,11 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>3.57531</v>
+        <v>3.407866</v>
       </c>
     </row>
     <row r="630">
@@ -14915,11 +14915,11 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>3.524301</v>
+        <v>3.414486</v>
       </c>
     </row>
     <row r="631">
@@ -14938,11 +14938,11 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>3.465361</v>
+        <v>3.459084</v>
       </c>
     </row>
     <row r="632">
@@ -14961,11 +14961,11 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>20260525</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>3.358616</v>
+        <v>3.532267</v>
       </c>
     </row>
     <row r="633">
@@ -14984,11 +14984,11 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>3.408954</v>
+        <v>3.537955</v>
       </c>
     </row>
     <row r="634">
@@ -15007,11 +15007,11 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>3.392661</v>
+        <v>3.477861</v>
       </c>
     </row>
     <row r="635">
@@ -15030,11 +15030,11 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>3.410886</v>
+        <v>3.591227</v>
       </c>
     </row>
     <row r="636">
@@ -15053,11 +15053,11 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>3.380955</v>
+        <v>3.555828</v>
       </c>
     </row>
     <row r="637">
@@ -15076,11 +15076,11 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>3.450091</v>
+        <v>3.614122</v>
       </c>
     </row>
     <row r="638">
@@ -15099,11 +15099,11 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>3.390251</v>
+        <v>3.57531</v>
       </c>
     </row>
     <row r="639">
@@ -15122,11 +15122,11 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>3.434872</v>
+        <v>3.524301</v>
       </c>
     </row>
     <row r="640">
@@ -15145,11 +15145,11 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>3.451103</v>
+        <v>3.465361</v>
       </c>
     </row>
     <row r="641">
@@ -15168,11 +15168,11 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260525</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>3.474414</v>
+        <v>3.358616</v>
       </c>
     </row>
     <row r="642">
@@ -15191,11 +15191,11 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>3.487726</v>
+        <v>3.408954</v>
       </c>
     </row>
     <row r="643">
@@ -15214,11 +15214,11 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>3.488064</v>
+        <v>3.392661</v>
       </c>
     </row>
     <row r="644">
@@ -15237,11 +15237,11 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>3.510348</v>
+        <v>3.410886</v>
       </c>
     </row>
     <row r="645">
@@ -15260,11 +15260,11 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>3.466867</v>
+        <v>3.380955</v>
       </c>
     </row>
     <row r="646">
@@ -15283,11 +15283,11 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>3.45513</v>
+        <v>3.450091</v>
       </c>
     </row>
     <row r="647">
@@ -15306,11 +15306,11 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>3.381408</v>
+        <v>3.390251</v>
       </c>
     </row>
     <row r="648">
@@ -15329,11 +15329,11 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>3.360241</v>
+        <v>3.434872</v>
       </c>
     </row>
     <row r="649">
@@ -15352,11 +15352,11 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>3.35235</v>
+        <v>3.451103</v>
       </c>
     </row>
     <row r="650">
@@ -15375,11 +15375,11 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>3.358799</v>
+        <v>3.474414</v>
       </c>
     </row>
     <row r="651">
@@ -15398,11 +15398,11 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>20260619</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>3.413209</v>
+        <v>3.487726</v>
       </c>
     </row>
     <row r="652">
@@ -15421,11 +15421,11 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>3.381184</v>
+        <v>3.488064</v>
       </c>
     </row>
     <row r="653">
@@ -15444,11 +15444,11 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>3.34561</v>
+        <v>3.510348</v>
       </c>
     </row>
     <row r="654">
@@ -15467,11 +15467,11 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>3.313304</v>
+        <v>3.466867</v>
       </c>
     </row>
     <row r="655">
@@ -15490,11 +15490,11 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>3.294135</v>
+        <v>3.45513</v>
       </c>
     </row>
     <row r="656">
@@ -15513,11 +15513,11 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>3.306326</v>
+        <v>3.381408</v>
       </c>
     </row>
     <row r="657">
@@ -15536,11 +15536,11 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>3.309678</v>
+        <v>3.360241</v>
       </c>
     </row>
     <row r="658">
@@ -15559,11 +15559,11 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>3.306024</v>
+        <v>3.35235</v>
       </c>
     </row>
     <row r="659">
@@ -15582,11 +15582,11 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>3.350751</v>
+        <v>3.358799</v>
       </c>
     </row>
     <row r="660">
@@ -15605,11 +15605,11 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260619</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>3.371501</v>
+        <v>3.413209</v>
       </c>
     </row>
     <row r="661">
@@ -15628,11 +15628,11 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>20260703</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>3.39017</v>
+        <v>3.381184</v>
       </c>
     </row>
     <row r="662">
@@ -15651,11 +15651,11 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>3.393866</v>
+        <v>3.34561</v>
       </c>
     </row>
     <row r="663">
@@ -15674,11 +15674,11 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>3.435339</v>
+        <v>3.313304</v>
       </c>
     </row>
     <row r="664">
@@ -15697,11 +15697,11 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>3.529697</v>
+        <v>3.294135</v>
       </c>
     </row>
     <row r="665">
@@ -15720,11 +15720,11 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>3.51885</v>
+        <v>3.306326</v>
       </c>
     </row>
     <row r="666">
@@ -15743,11 +15743,11 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>3.497131</v>
+        <v>3.309678</v>
       </c>
     </row>
     <row r="667">
@@ -15766,11 +15766,11 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>3.516607</v>
+        <v>3.306024</v>
       </c>
     </row>
     <row r="668">
@@ -15789,11 +15789,11 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>3.544458</v>
+        <v>3.350751</v>
       </c>
     </row>
     <row r="669">
@@ -15812,11 +15812,11 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>3.562378</v>
+        <v>3.371501</v>
       </c>
     </row>
     <row r="670">
@@ -15835,11 +15835,11 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260703</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>3.595451</v>
+        <v>3.39017</v>
       </c>
     </row>
     <row r="671">
@@ -15858,11 +15858,11 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>20260717</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>3.569517</v>
+        <v>3.393866</v>
       </c>
     </row>
     <row r="672">
@@ -15881,11 +15881,11 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>20260720</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>3.581423</v>
+        <v>3.435339</v>
       </c>
     </row>
     <row r="673">
@@ -15904,11 +15904,11 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>20260721</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>3.629988</v>
+        <v>3.529697</v>
       </c>
     </row>
     <row r="674">
@@ -15927,11 +15927,11 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>20260722</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>3.627083</v>
+        <v>3.51885</v>
       </c>
     </row>
     <row r="675">
@@ -15950,11 +15950,11 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>20260723</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>3.651615</v>
+        <v>3.497131</v>
       </c>
     </row>
     <row r="676">
@@ -15973,11 +15973,11 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>20260724</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>3.625742</v>
+        <v>3.516607</v>
       </c>
     </row>
     <row r="677">
@@ -15996,11 +15996,11 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>20260727</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>3.577342</v>
+        <v>3.544458</v>
       </c>
     </row>
     <row r="678">
@@ -16019,11 +16019,11 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>20260728</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>3.573321</v>
+        <v>3.562378</v>
       </c>
     </row>
     <row r="679">
@@ -16042,11 +16042,11 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>20260729</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>3.592969</v>
+        <v>3.595451</v>
       </c>
     </row>
     <row r="680">
@@ -16065,11 +16065,11 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>20260730</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>3.618198</v>
+        <v>3.569517</v>
       </c>
     </row>
     <row r="681">
@@ -16088,11 +16088,11 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>20260731</t>
+          <t>20260720</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>3.639713</v>
+        <v>3.581423</v>
       </c>
     </row>
     <row r="682">
@@ -16111,11 +16111,11 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>20260803</t>
+          <t>20260721</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>3.584459</v>
+        <v>3.629988</v>
       </c>
     </row>
     <row r="683">
@@ -16134,11 +16134,11 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>20260804</t>
+          <t>20260722</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>3.536361</v>
+        <v>3.627083</v>
       </c>
     </row>
     <row r="684">
@@ -16157,11 +16157,241 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
+          <t>20260723</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>3.651615</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>10</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>20260724</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>3.625742</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>10</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>3.577342</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>10</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>3.573321</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>10</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>20260729</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>3.592969</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>10</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>20260730</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>3.618198</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>10</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>20260731</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>3.639713</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>10</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>3.584459</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>10</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>3.536361</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>10</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
           <t>20260805</t>
         </is>
       </c>
-      <c r="E684" t="n">
+      <c r="E693" t="n">
         <v>3.543432</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>10</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>YC.B.U2.EUR.4F.G_N_C.SV_C_YM.SR_10Y</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>유로존 국채금리 10년</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>3.547646</v>
       </c>
     </row>
   </sheetData>
